--- a/output/2026-10-02_01_Malesia_Melaka_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-10-02_01_Malesia_Melaka_Componentistica_Ventilazione_industriale.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Distributore industriale MRO (SSM 874276-V) con catalogo dedicato "VENTILATION" e "Dust Collector" (es. JETMAC JDC1900, HITZ, EUROX); verificato su sito ufficiale e fonti terze (Experian/ZoomInfo).</t>
+          <t>Distributore industriale MRO (SSM 874276-V) con catalogo dedicato "VENTILATION" e "Dust Collector" (es. JETMAC JDC1900, HITZ, EUROX); verificato su sito ufficiale e fonti terze (Experian/ZoomInfo). [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
